--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
         <v>18</v>
@@ -3809,82 +3809,82 @@
         <v>0.05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="G8" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="H8" t="n">
-        <v>104.68</v>
+        <v>99.45</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>62.58</v>
+        <v>59.45</v>
       </c>
       <c r="N8" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="O8" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="P8" t="n">
-        <v>6.89</v>
+        <v>7.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>4.42</v>
+        <v>4.75</v>
       </c>
       <c r="S8" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>55.26</v>
+        <v>54.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.79</v>
+        <v>11.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.53</v>
+        <v>6.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.26</v>
+        <v>5.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>13.84</v>
+        <v>14.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,67 +3968,67 @@
         <v>2.17</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.08</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="BL8" t="n">
         <v>0.76</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS8" t="n">
-        <v>67.56999999999999</v>
+        <v>68.42</v>
       </c>
       <c r="BT8" t="n">
-        <v>45.95</v>
+        <v>47.37</v>
       </c>
       <c r="BU8" t="n">
-        <v>21.62</v>
+        <v>21.05</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.109999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BX8" t="n">
-        <v>56.76</v>
+        <v>57.89</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="BZ8" t="n">
         <v>2.27</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.09</v>
+        <v>3.01</v>
       </c>
       <c r="CB8" t="n">
         <v>3.48</v>
@@ -4040,43 +4040,43 @@
         <v>2.54</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="CR8" t="n">
         <v>1.46</v>
@@ -4088,7 +4088,7 @@
         <v>2.74</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV8" t="n">
         <v>1.83</v>
@@ -4121,76 +4121,76 @@
         <v>0.03</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DH8" t="n">
-        <v>100.4</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="DM8" t="n">
-        <v>59.35</v>
+        <v>57.79</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="DP8" t="n">
-        <v>5.62</v>
+        <v>5.9</v>
       </c>
       <c r="DQ8" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="DR8" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU8" t="n">
         <v>0.03</v>
       </c>
       <c r="DV8" t="n">
-        <v>55.65</v>
+        <v>55.29</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.08</v>
+        <v>11.1</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.33</v>
+        <v>6.42</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.75</v>
+        <v>4.68</v>
       </c>
       <c r="EA8" t="n">
-        <v>12.11</v>
+        <v>12.32</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="9">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
         <v>0.16</v>
@@ -5099,136 +5099,136 @@
         <v>0.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="AI11" t="n">
-        <v>111.26</v>
+        <v>105.7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="AL11" t="n">
-        <v>5.53</v>
+        <v>5.75</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>72.63</v>
+        <v>69</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.32</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="AT11" t="n">
         <v>1.05</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="AX11" t="n">
         <v>0.05</v>
       </c>
       <c r="AY11" t="n">
-        <v>55.16</v>
+        <v>55.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.53</v>
+        <v>13.85</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.210000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.32</v>
+        <v>5.45</v>
       </c>
       <c r="BD11" t="n">
-        <v>15.89</v>
+        <v>16.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.16</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.61</v>
+        <v>4.46</v>
       </c>
       <c r="BR11" t="n">
-        <v>97.37</v>
+        <v>97.44</v>
       </c>
       <c r="BS11" t="n">
-        <v>84.20999999999999</v>
+        <v>84.62</v>
       </c>
       <c r="BT11" t="n">
-        <v>47.37</v>
+        <v>48.72</v>
       </c>
       <c r="BU11" t="n">
-        <v>23.68</v>
+        <v>23.08</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.89</v>
+        <v>7.69</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="BX11" t="n">
-        <v>47.37</v>
+        <v>48.72</v>
       </c>
       <c r="BY11" t="n">
         <v>1.4</v>
@@ -5237,55 +5237,55 @@
         <v>1.49</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="CB11" t="n">
         <v>4.31</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="CD11" t="n">
         <v>1.9</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
@@ -5327,79 +5327,79 @@
         <v>3.74</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="DH11" t="n">
-        <v>117.71</v>
+        <v>114.69</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.79</v>
+        <v>5.9</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="DM11" t="n">
-        <v>72.05</v>
+        <v>70.2</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="DP11" t="n">
-        <v>6.18</v>
+        <v>6.54</v>
       </c>
       <c r="DQ11" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="DR11" t="n">
-        <v>3.61</v>
+        <v>3.79</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="DV11" t="n">
-        <v>56.68</v>
+        <v>56.72</v>
       </c>
       <c r="DW11" t="n">
         <v>0.18</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.74</v>
+        <v>13.9</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.369999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.37</v>
+        <v>5.44</v>
       </c>
       <c r="EA11" t="n">
-        <v>15.24</v>
+        <v>15.51</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
         <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
         <v>0.25</v>
@@ -4693,139 +4693,139 @@
         <v>2.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="AI10" t="n">
-        <v>100.61</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="AL10" t="n">
-        <v>5.22</v>
+        <v>4.95</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AN10" t="n">
-        <v>70.39</v>
+        <v>69.47</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.89</v>
+        <v>7.68</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.28</v>
+        <v>5.47</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>53.94</v>
+        <v>53.05</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.11</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.56</v>
+        <v>12.26</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.83</v>
+        <v>7.68</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.72</v>
+        <v>4.58</v>
       </c>
       <c r="BD10" t="n">
-        <v>14</v>
+        <v>14.05</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.61</v>
+        <v>2.79</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.470000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="BJ10" t="n">
         <v>0.82</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="BQ10" t="n">
         <v>5.21</v>
       </c>
       <c r="BR10" t="n">
-        <v>84.20999999999999</v>
+        <v>84.62</v>
       </c>
       <c r="BS10" t="n">
-        <v>76.31999999999999</v>
+        <v>76.92</v>
       </c>
       <c r="BT10" t="n">
-        <v>63.16</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="BU10" t="n">
-        <v>36.84</v>
+        <v>38.46</v>
       </c>
       <c r="BV10" t="n">
-        <v>15.79</v>
+        <v>15.38</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.89</v>
+        <v>7.69</v>
       </c>
       <c r="BX10" t="n">
-        <v>57.89</v>
+        <v>58.97</v>
       </c>
       <c r="BY10" t="n">
         <v>2.55</v>
@@ -4834,55 +4834,55 @@
         <v>1.57</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="CC10" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="CD10" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="CF10" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CQ10" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
@@ -4903,100 +4903,100 @@
         <v>2.13</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="DG10" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="DH10" t="n">
-        <v>106.34</v>
+        <v>105.8</v>
       </c>
       <c r="DI10" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.58</v>
+        <v>2.67</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.68</v>
+        <v>5.54</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DM10" t="n">
-        <v>70.23999999999999</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="DP10" t="n">
-        <v>7.58</v>
+        <v>7.95</v>
       </c>
       <c r="DQ10" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU10" t="n">
         <v>-0.03</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.18</v>
+        <v>53.74</v>
       </c>
       <c r="DW10" t="n">
         <v>0.03</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.5</v>
+        <v>12.36</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.52</v>
+        <v>7.46</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.97</v>
+        <v>4.9</v>
       </c>
       <c r="EA10" t="n">
-        <v>14.16</v>
+        <v>14.18</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
         <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F11" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
-        <v>124.16</v>
+        <v>123</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="K11" t="n">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="M11" t="n">
-        <v>71.47</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="O11" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="T11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>58.21</v>
+        <v>58.45</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.95</v>
+        <v>14.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.529999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.42</v>
+        <v>5.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>14.58</v>
+        <v>15.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
         <v>0.05</v>
@@ -5177,70 +5177,70 @@
         <v>2.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.279999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="BL11" t="n">
         <v>0.85</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.46</v>
+        <v>4.47</v>
       </c>
       <c r="BR11" t="n">
-        <v>97.44</v>
+        <v>97.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>84.62</v>
+        <v>85</v>
       </c>
       <c r="BT11" t="n">
-        <v>48.72</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>23.08</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.69</v>
+        <v>7.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>48.72</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.31</v>
+        <v>4.25</v>
       </c>
       <c r="CC11" t="n">
         <v>1.66</v>
@@ -5249,43 +5249,43 @@
         <v>1.9</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CG11" t="n">
         <v>2.32</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.83</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL11" t="n">
         <v>1.78</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CO11" t="n">
         <v>1.19</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
@@ -5306,67 +5306,67 @@
         <v>2.25</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="DE11" t="n">
         <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="DH11" t="n">
-        <v>114.69</v>
+        <v>114.35</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.9</v>
+        <v>5.92</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DM11" t="n">
         <v>70.2</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DP11" t="n">
-        <v>6.54</v>
+        <v>6.75</v>
       </c>
       <c r="DQ11" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="DR11" t="n">
-        <v>3.79</v>
+        <v>3.82</v>
       </c>
       <c r="DS11" t="n">
         <v>0.18</v>
@@ -5375,31 +5375,31 @@
         <v>0.15</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DV11" t="n">
-        <v>56.72</v>
+        <v>56.88</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.9</v>
+        <v>14.05</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.460000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.44</v>
+        <v>5.48</v>
       </c>
       <c r="EA11" t="n">
-        <v>15.51</v>
+        <v>15.88</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
         <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="F10" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H10" t="n">
-        <v>111.5</v>
+        <v>112.14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="K10" t="n">
-        <v>6.1</v>
+        <v>6.14</v>
       </c>
       <c r="L10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>70.09999999999999</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.9</v>
       </c>
-      <c r="O10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="R10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.95</v>
-      </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="U10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W10" t="n">
         <v>-0.05</v>
       </c>
       <c r="X10" t="n">
-        <v>54.4</v>
+        <v>54.43</v>
       </c>
       <c r="Y10" t="n">
         <v>-0.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.45</v>
+        <v>12.48</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.25</v>
+        <v>7.19</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.2</v>
+        <v>5.29</v>
       </c>
       <c r="AC10" t="n">
-        <v>14.3</v>
+        <v>13.57</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AF10" t="n">
         <v>0.16</v>
@@ -4774,70 +4774,70 @@
         <v>2.79</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.41</v>
+        <v>9.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="BR10" t="n">
-        <v>84.62</v>
+        <v>85</v>
       </c>
       <c r="BS10" t="n">
-        <v>76.92</v>
+        <v>75</v>
       </c>
       <c r="BT10" t="n">
-        <v>64.09999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>38.46</v>
+        <v>37.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>15.38</v>
+        <v>15</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.69</v>
+        <v>7.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>58.97</v>
+        <v>57.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.37</v>
+        <v>4.31</v>
       </c>
       <c r="CC10" t="n">
         <v>1.73</v>
@@ -4846,124 +4846,124 @@
         <v>1.91</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="CF10" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.66</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CV10" t="n">
         <v>1.77</v>
       </c>
-      <c r="CR10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="CU10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CV10" t="n">
-        <v>1.75</v>
-      </c>
       <c r="CW10" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CX10" t="n">
         <v>1.55</v>
       </c>
       <c r="CY10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DA10" t="n">
         <v>1.9</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="DA10" t="n">
-        <v>1.91</v>
       </c>
       <c r="DB10" t="n">
         <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="DH10" t="n">
-        <v>105.8</v>
+        <v>106.27</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.54</v>
+        <v>5.57</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="DM10" t="n">
-        <v>69.79000000000001</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DP10" t="n">
-        <v>7.95</v>
+        <v>7.72</v>
       </c>
       <c r="DQ10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.77</v>
+        <v>4.62</v>
       </c>
       <c r="DS10" t="n">
         <v>0.2</v>
@@ -4975,28 +4975,28 @@
         <v>-0.03</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.74</v>
+        <v>53.77</v>
       </c>
       <c r="DW10" t="n">
         <v>0.03</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.36</v>
+        <v>12.38</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.46</v>
+        <v>7.42</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="EA10" t="n">
-        <v>14.18</v>
+        <v>13.8</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
         <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" t="n">
         <v>0.15</v>
@@ -5099,52 +5099,52 @@
         <v>0.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="AI11" t="n">
-        <v>105.7</v>
+        <v>106.48</v>
       </c>
       <c r="AJ11" t="n">
         <v>0.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AL11" t="n">
-        <v>5.75</v>
+        <v>5.57</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="AN11" t="n">
-        <v>69</v>
+        <v>69.38</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7</v>
+        <v>6.62</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="AT11" t="n">
         <v>1.05</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AW11" t="n">
         <v>0.1</v>
@@ -5153,82 +5153,82 @@
         <v>0.05</v>
       </c>
       <c r="AY11" t="n">
-        <v>55.3</v>
+        <v>54.81</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.85</v>
+        <v>13.38</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.4</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.45</v>
+        <v>5.24</v>
       </c>
       <c r="BD11" t="n">
-        <v>16.4</v>
+        <v>15.57</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="BH11" t="n">
         <v>9.220000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="BL11" t="n">
         <v>0.85</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.47</v>
+        <v>4.49</v>
       </c>
       <c r="BR11" t="n">
-        <v>97.5</v>
+        <v>97.56</v>
       </c>
       <c r="BS11" t="n">
-        <v>85</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>48.78</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>24.39</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.5</v>
+        <v>7.32</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>48.78</v>
       </c>
       <c r="BY11" t="n">
         <v>1.43</v>
@@ -5237,22 +5237,22 @@
         <v>1.55</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CG11" t="n">
         <v>2.32</v>
@@ -5261,31 +5261,31 @@
         <v>1.16</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.83</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP11" t="n">
         <v>1.9</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
@@ -5294,16 +5294,16 @@
         <v>3.07</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CU11" t="n">
         <v>1.38</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CX11" t="n">
         <v>1.64</v>
@@ -5324,82 +5324,82 @@
         <v>2.12</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="DE11" t="n">
         <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="DH11" t="n">
-        <v>114.35</v>
+        <v>114.54</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.92</v>
+        <v>5.83</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="DM11" t="n">
-        <v>70.2</v>
+        <v>70.37</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="DP11" t="n">
-        <v>6.75</v>
+        <v>6.56</v>
       </c>
       <c r="DQ11" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DR11" t="n">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT11" t="n">
         <v>0.15</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="DV11" t="n">
-        <v>56.88</v>
+        <v>56.59</v>
       </c>
       <c r="DW11" t="n">
         <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.05</v>
+        <v>13.8</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.57</v>
+        <v>8.44</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.48</v>
+        <v>5.37</v>
       </c>
       <c r="EA11" t="n">
-        <v>15.88</v>
+        <v>15.46</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
@@ -4885,16 +4885,16 @@
         <v>1.83</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CV10" t="n">
         <v>1.77</v>
@@ -5099,7 +5099,7 @@
         <v>0.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="AH11" t="n">
         <v>2.57</v>
@@ -5111,7 +5111,7 @@
         <v>0.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="AL11" t="n">
         <v>5.57</v>
@@ -5174,7 +5174,7 @@
         <v>1.63</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="BG11" t="n">
         <v>2.63</v>
@@ -5294,7 +5294,7 @@
         <v>3.07</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CU11" t="n">
         <v>1.38</v>
@@ -5330,7 +5330,7 @@
         <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="DG11" t="n">
         <v>2.97</v>
@@ -5342,7 +5342,7 @@
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DK11" t="n">
         <v>5.83</v>
@@ -5399,7 +5399,7 @@
         <v>1.68</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
         <v>0.11</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="AI3" t="n">
-        <v>87.84</v>
+        <v>89.28</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.89</v>
+        <v>4.06</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>45.21</v>
+        <v>45.94</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.74</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.89</v>
+        <v>5.22</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="AV3" t="n">
         <v>0.11</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.32</v>
+        <v>44.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.32</v>
+        <v>7.56</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.79</v>
+        <v>5</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BD3" t="n">
-        <v>13.84</v>
+        <v>14.67</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.51</v>
+        <v>8.69</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.62</v>
+        <v>3.69</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.68</v>
+        <v>4.78</v>
       </c>
       <c r="BR3" t="n">
-        <v>81.08</v>
+        <v>80.56</v>
       </c>
       <c r="BS3" t="n">
-        <v>59.46</v>
+        <v>58.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>40.54</v>
+        <v>38.89</v>
       </c>
       <c r="BU3" t="n">
-        <v>13.51</v>
+        <v>11.11</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.41</v>
+        <v>5.56</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="BX3" t="n">
-        <v>45.95</v>
+        <v>44.44</v>
       </c>
       <c r="BY3" t="n">
         <v>3.26</v>
@@ -2013,13 +2013,13 @@
         <v>4.3</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CB3" t="n">
         <v>3.45</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.63</v>
+        <v>4.44</v>
       </c>
       <c r="CD3" t="n">
         <v>5.32</v>
@@ -2031,7 +2031,7 @@
         <v>3.19</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CH3" t="n">
         <v>1.17</v>
@@ -2040,13 +2040,13 @@
         <v>1.49</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM3" t="n">
         <v>1.93</v>
@@ -2058,10 +2058,10 @@
         <v>1.36</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.29</v>
+        <v>4.31</v>
       </c>
       <c r="CR3" t="n">
         <v>1.54</v>
@@ -2103,46 +2103,46 @@
         <v>5.06</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="DH3" t="n">
-        <v>84.13</v>
+        <v>84.75</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="DM3" t="n">
-        <v>47.4</v>
+        <v>47.83</v>
       </c>
       <c r="DN3" t="n">
         <v>1</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DP3" t="n">
-        <v>7.19</v>
+        <v>7.42</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.54</v>
+        <v>4.69</v>
       </c>
       <c r="DS3" t="n">
         <v>0.14</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="DX3" t="n">
-        <v>7.03</v>
+        <v>7.14</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.38</v>
+        <v>4.47</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="EA3" t="n">
-        <v>11.89</v>
+        <v>12.25</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="EC3" t="n">
         <v>3.06</v>
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
         <v>21</v>
       </c>
       <c r="E11" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="H11" t="n">
-        <v>123</v>
+        <v>125.63</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>6.1</v>
+        <v>6.37</v>
       </c>
       <c r="L11" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="M11" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="N11" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="O11" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="P11" t="n">
-        <v>6.5</v>
+        <v>6.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="R11" t="n">
-        <v>4.1</v>
+        <v>4.37</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="T11" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>58.45</v>
+        <v>58.42</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.25</v>
+        <v>14.53</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.75</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.5</v>
+        <v>5.58</v>
       </c>
       <c r="AC11" t="n">
-        <v>15.35</v>
+        <v>16.21</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AF11" t="n">
         <v>0.05</v>
@@ -5177,67 +5177,67 @@
         <v>2.81</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.220000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BL11" t="n">
         <v>0.85</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.49</v>
+        <v>4.58</v>
       </c>
       <c r="BR11" t="n">
-        <v>97.56</v>
+        <v>97.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>82.93000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>48.78</v>
+        <v>47.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>24.39</v>
+        <v>22.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.32</v>
+        <v>7.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>48.78</v>
+        <v>47.5</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="BZ11" t="n">
         <v>1.55</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB11" t="n">
         <v>4.19</v>
@@ -5249,10 +5249,10 @@
         <v>2.04</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CG11" t="n">
         <v>2.32</v>
@@ -5261,13 +5261,13 @@
         <v>1.16</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL11" t="n">
         <v>1.79</v>
@@ -5279,13 +5279,13 @@
         <v>1.39</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP11" t="n">
         <v>1.9</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
@@ -5327,79 +5327,79 @@
         <v>3.81</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="DH11" t="n">
-        <v>114.54</v>
+        <v>115.58</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.83</v>
+        <v>5.95</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="DM11" t="n">
-        <v>70.37</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="DP11" t="n">
-        <v>6.56</v>
+        <v>6.75</v>
       </c>
       <c r="DQ11" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DR11" t="n">
-        <v>3.71</v>
+        <v>3.82</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0.03</v>
       </c>
       <c r="DV11" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="DW11" t="n">
         <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.8</v>
+        <v>13.93</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.44</v>
+        <v>8.52</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.37</v>
+        <v>5.4</v>
       </c>
       <c r="EA11" t="n">
-        <v>15.46</v>
+        <v>15.87</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" t="n">
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
         <v>0.11</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="AI3" t="n">
-        <v>89.28</v>
+        <v>87.84</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.06</v>
+        <v>3.89</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="AN3" t="n">
-        <v>45.94</v>
+        <v>45.21</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.279999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.22</v>
+        <v>4.89</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="AV3" t="n">
         <v>0.11</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.5</v>
+        <v>44.32</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.56</v>
+        <v>7.32</v>
       </c>
       <c r="BB3" t="n">
-        <v>5</v>
+        <v>4.79</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BD3" t="n">
-        <v>14.67</v>
+        <v>13.84</v>
       </c>
       <c r="BE3" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.69</v>
+        <v>8.51</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.69</v>
+        <v>3.57</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.78</v>
+        <v>4.62</v>
       </c>
       <c r="BR3" t="n">
-        <v>80.56</v>
+        <v>81.08</v>
       </c>
       <c r="BS3" t="n">
-        <v>58.33</v>
+        <v>59.46</v>
       </c>
       <c r="BT3" t="n">
-        <v>38.89</v>
+        <v>40.54</v>
       </c>
       <c r="BU3" t="n">
-        <v>11.11</v>
+        <v>13.51</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BX3" t="n">
-        <v>44.44</v>
+        <v>45.95</v>
       </c>
       <c r="BY3" t="n">
         <v>3.26</v>
@@ -2013,13 +2013,13 @@
         <v>4.3</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="CB3" t="n">
         <v>3.45</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.44</v>
+        <v>4.63</v>
       </c>
       <c r="CD3" t="n">
         <v>5.32</v>
@@ -2031,7 +2031,7 @@
         <v>3.19</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CH3" t="n">
         <v>1.17</v>
@@ -2040,13 +2040,13 @@
         <v>1.49</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM3" t="n">
         <v>1.93</v>
@@ -2058,10 +2058,10 @@
         <v>1.36</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="CR3" t="n">
         <v>1.54</v>
@@ -2103,46 +2103,46 @@
         <v>5.06</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="DH3" t="n">
-        <v>84.75</v>
+        <v>84.13</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM3" t="n">
-        <v>47.83</v>
+        <v>47.4</v>
       </c>
       <c r="DN3" t="n">
         <v>1</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="DP3" t="n">
-        <v>7.42</v>
+        <v>7.19</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.69</v>
+        <v>4.54</v>
       </c>
       <c r="DS3" t="n">
         <v>0.14</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX3" t="n">
-        <v>7.14</v>
+        <v>7.03</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.47</v>
+        <v>4.38</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="EA3" t="n">
-        <v>12.25</v>
+        <v>11.89</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="EC3" t="n">
         <v>3.06</v>
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
         <v>21</v>
       </c>
       <c r="E11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F11" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="n">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="H11" t="n">
-        <v>125.63</v>
+        <v>123</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K11" t="n">
-        <v>6.37</v>
+        <v>6.1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="M11" t="n">
-        <v>73</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="O11" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="P11" t="n">
-        <v>6.89</v>
+        <v>6.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
-        <v>4.37</v>
+        <v>4.1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="T11" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="U11" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>58.42</v>
+        <v>58.45</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.53</v>
+        <v>14.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.949999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.58</v>
+        <v>5.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.21</v>
+        <v>15.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
         <v>0.05</v>
@@ -5177,67 +5177,67 @@
         <v>2.81</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.4</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="BL11" t="n">
         <v>0.85</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.58</v>
+        <v>4.44</v>
       </c>
       <c r="BR11" t="n">
-        <v>97.5</v>
+        <v>97.56</v>
       </c>
       <c r="BS11" t="n">
-        <v>82.5</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>47.5</v>
+        <v>48.78</v>
       </c>
       <c r="BU11" t="n">
-        <v>22.5</v>
+        <v>24.39</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.5</v>
+        <v>7.32</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BX11" t="n">
-        <v>47.5</v>
+        <v>48.78</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BZ11" t="n">
         <v>1.55</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="CB11" t="n">
         <v>4.19</v>
@@ -5249,10 +5249,10 @@
         <v>2.04</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CG11" t="n">
         <v>2.32</v>
@@ -5261,13 +5261,13 @@
         <v>1.16</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL11" t="n">
         <v>1.79</v>
@@ -5279,13 +5279,13 @@
         <v>1.39</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP11" t="n">
         <v>1.9</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
@@ -5327,79 +5327,79 @@
         <v>3.81</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.03</v>
+        <v>2.93</v>
       </c>
       <c r="DH11" t="n">
-        <v>115.58</v>
+        <v>114.54</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.95</v>
+        <v>5.83</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DM11" t="n">
-        <v>71.09999999999999</v>
+        <v>70.37</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="DP11" t="n">
-        <v>6.75</v>
+        <v>6.56</v>
       </c>
       <c r="DQ11" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DR11" t="n">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="DS11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DT11" t="n">
         <v>0.15</v>
-      </c>
-      <c r="DT11" t="n">
-        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0.03</v>
       </c>
       <c r="DV11" t="n">
-        <v>56.52</v>
+        <v>56.59</v>
       </c>
       <c r="DW11" t="n">
         <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.93</v>
+        <v>13.8</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.52</v>
+        <v>8.44</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.4</v>
+        <v>5.37</v>
       </c>
       <c r="EA11" t="n">
-        <v>15.87</v>
+        <v>15.46</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
@@ -1421,13 +1421,13 @@
         <v>2.16</v>
       </c>
       <c r="P2" t="n">
-        <v>6.84</v>
+        <v>7.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="R2" t="n">
-        <v>4.32</v>
+        <v>5.21</v>
       </c>
       <c r="S2" t="n">
         <v>0.84</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>53.21</v>
+        <v>53.63</v>
       </c>
       <c r="Y2" t="n">
         <v>0.05</v>
@@ -1454,16 +1454,16 @@
         <v>8.84</v>
       </c>
       <c r="AA2" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.84</v>
+        <v>3.89</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.89</v>
+        <v>13.89</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
         <v>2.68</v>
@@ -1733,13 +1733,13 @@
         <v>1.87</v>
       </c>
       <c r="DP2" t="n">
-        <v>6.65</v>
+        <v>7.05</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="DR2" t="n">
-        <v>4.89</v>
+        <v>5.35</v>
       </c>
       <c r="DS2" t="n">
         <v>0.09</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.57</v>
+        <v>53.78</v>
       </c>
       <c r="DW2" t="n">
         <v>0.08</v>
@@ -1760,13 +1760,13 @@
         <v>8.130000000000001</v>
       </c>
       <c r="DY2" t="n">
-        <v>4.89</v>
+        <v>4.87</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="EA2" t="n">
-        <v>12.97</v>
+        <v>13.49</v>
       </c>
       <c r="EB2" t="n">
         <v>1.13</v>
@@ -1794,7 +1794,7 @@
         <v>0.11</v>
       </c>
       <c r="F3" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="G3" t="n">
         <v>1.44</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="K3" t="n">
         <v>2.89</v>
@@ -1869,13 +1869,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="AH3" t="n">
         <v>2.26</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="AL3" t="n">
         <v>3.89</v>
@@ -1905,13 +1905,13 @@
         <v>1.47</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.74</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.89</v>
+        <v>5.58</v>
       </c>
       <c r="AT3" t="n">
         <v>1.47</v>
@@ -1929,28 +1929,28 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.32</v>
+        <v>44.37</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.26</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.32</v>
+        <v>7.37</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.79</v>
+        <v>4.89</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="BD3" t="n">
-        <v>13.84</v>
+        <v>15.11</v>
       </c>
       <c r="BE3" t="n">
         <v>0.97</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="BG3" t="n">
         <v>2.03</v>
@@ -2106,7 +2106,7 @@
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="DG3" t="n">
         <v>1.86</v>
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="DK3" t="n">
         <v>3.4</v>
@@ -2136,13 +2136,13 @@
         <v>1.57</v>
       </c>
       <c r="DP3" t="n">
-        <v>7.19</v>
+        <v>7.6</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.54</v>
+        <v>4.89</v>
       </c>
       <c r="DS3" t="n">
         <v>0.14</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.6</v>
+        <v>44.62</v>
       </c>
       <c r="DW3" t="n">
         <v>0.27</v>
       </c>
       <c r="DX3" t="n">
-        <v>7.03</v>
+        <v>7.05</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.38</v>
+        <v>4.43</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="EA3" t="n">
-        <v>11.89</v>
+        <v>12.54</v>
       </c>
       <c r="EB3" t="n">
         <v>0.96</v>
       </c>
       <c r="EC3" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="4">
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="n">
         <v>1.67</v>
@@ -2290,7 +2290,7 @@
         <v>0.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="AL4" t="n">
         <v>3.83</v>
@@ -2353,7 +2353,7 @@
         <v>1.29</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="BG4" t="n">
         <v>2.22</v>
@@ -2509,7 +2509,7 @@
         <v>0.03</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="DG4" t="n">
         <v>2.03</v>
@@ -2521,7 +2521,7 @@
         <v>0.09</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="DK4" t="n">
         <v>4.03</v>
@@ -2578,7 +2578,7 @@
         <v>1.34</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="5">
@@ -2630,13 +2630,13 @@
         <v>2.67</v>
       </c>
       <c r="P5" t="n">
-        <v>5.61</v>
+        <v>6.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="R5" t="n">
-        <v>3.83</v>
+        <v>4.39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -2660,19 +2660,19 @@
         <v>0.06</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.94</v>
+        <v>10.17</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.22</v>
+        <v>6.44</v>
       </c>
       <c r="AB5" t="n">
         <v>3.72</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.94</v>
+        <v>12.39</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE5" t="n">
         <v>2.11</v>
@@ -2711,13 +2711,13 @@
         <v>2.16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.11</v>
+        <v>7.47</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.95</v>
+        <v>4.21</v>
       </c>
       <c r="AT5" t="n">
         <v>1.21</v>
@@ -2735,25 +2735,25 @@
         <v>-0.05</v>
       </c>
       <c r="AY5" t="n">
-        <v>47.11</v>
+        <v>46.68</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.26</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>6.26</v>
       </c>
       <c r="BC5" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.47</v>
+        <v>18.42</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BF5" t="n">
         <v>2.26</v>
@@ -2942,13 +2942,13 @@
         <v>2.41</v>
       </c>
       <c r="DP5" t="n">
-        <v>6.38</v>
+        <v>6.86</v>
       </c>
       <c r="DQ5" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="DR5" t="n">
-        <v>3.89</v>
+        <v>4.3</v>
       </c>
       <c r="DS5" t="n">
         <v>0.09</v>
@@ -2960,25 +2960,25 @@
         <v>-0.03</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.57</v>
+        <v>49.35</v>
       </c>
       <c r="DW5" t="n">
         <v>0.16</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.460000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.11</v>
+        <v>6.35</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="EA5" t="n">
-        <v>14.29</v>
+        <v>15.49</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="EC5" t="n">
         <v>2.19</v>
@@ -3003,7 +3003,7 @@
         <v>0.05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="G6" t="n">
         <v>2.37</v>
@@ -3015,7 +3015,7 @@
         <v>0.05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>4.47</v>
@@ -3078,7 +3078,7 @@
         <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="AF6" t="n">
         <v>0.17</v>
@@ -3315,7 +3315,7 @@
         <v>0.11</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DG6" t="n">
         <v>2.14</v>
@@ -3327,7 +3327,7 @@
         <v>0.03</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="DK6" t="n">
         <v>4.21</v>
@@ -3384,7 +3384,7 @@
         <v>1.3</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="7">
@@ -3406,7 +3406,7 @@
         <v>0.11</v>
       </c>
       <c r="F7" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="G7" t="n">
         <v>2.16</v>
@@ -3418,7 +3418,7 @@
         <v>-0.16</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="K7" t="n">
         <v>4.42</v>
@@ -3436,13 +3436,13 @@
         <v>2.21</v>
       </c>
       <c r="P7" t="n">
-        <v>5.47</v>
+        <v>5.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.32</v>
+        <v>0.53</v>
       </c>
       <c r="R7" t="n">
-        <v>4.26</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -3460,25 +3460,25 @@
         <v>-0.26</v>
       </c>
       <c r="X7" t="n">
-        <v>51.53</v>
+        <v>51.47</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.21</v>
+        <v>-0.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.32</v>
+        <v>9.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.58</v>
+        <v>5.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.16</v>
+        <v>12.53</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
         <v>0.95</v>
@@ -3490,7 +3490,7 @@
         <v>1.39</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="AI7" t="n">
         <v>100.56</v>
@@ -3505,7 +3505,7 @@
         <v>4.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="AN7" t="n">
         <v>59.44</v>
@@ -3514,7 +3514,7 @@
         <v>0.22</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AQ7" t="n">
         <v>5.89</v>
@@ -3592,10 +3592,10 @@
         <v>0.89</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.59</v>
+        <v>4.38</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.7</v>
+        <v>4.54</v>
       </c>
       <c r="BR7" t="n">
         <v>89.19</v>
@@ -3718,10 +3718,10 @@
         <v>0.06</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="DH7" t="n">
         <v>104.22</v>
@@ -3730,13 +3730,13 @@
         <v>-0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DK7" t="n">
         <v>4.46</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="DM7" t="n">
         <v>62.59</v>
@@ -3745,16 +3745,16 @@
         <v>0.19</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DP7" t="n">
-        <v>5.67</v>
+        <v>5.89</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.49</v>
+        <v>0.6</v>
       </c>
       <c r="DR7" t="n">
-        <v>4.67</v>
+        <v>5.05</v>
       </c>
       <c r="DS7" t="n">
         <v>-0.08</v>
@@ -3766,25 +3766,25 @@
         <v>-0.19</v>
       </c>
       <c r="DV7" t="n">
-        <v>51</v>
+        <v>50.97</v>
       </c>
       <c r="DW7" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>9.08</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.62</v>
+        <v>5.81</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="EA7" t="n">
-        <v>12</v>
+        <v>12.71</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC7" t="n">
         <v>1.32</v>
@@ -3812,7 +3812,7 @@
         <v>1.85</v>
       </c>
       <c r="G8" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="H8" t="n">
         <v>99.45</v>
@@ -3821,13 +3821,13 @@
         <v>0.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="K8" t="n">
         <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="M8" t="n">
         <v>59.45</v>
@@ -3836,7 +3836,7 @@
         <v>0.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="P8" t="n">
         <v>7.35</v>
@@ -3995,10 +3995,10 @@
         <v>1.05</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.13</v>
+        <v>2.92</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="BR8" t="n">
         <v>92.11</v>
@@ -4124,7 +4124,7 @@
         <v>1.6</v>
       </c>
       <c r="DG8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DH8" t="n">
         <v>97.76000000000001</v>
@@ -4133,13 +4133,13 @@
         <v>0.1</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="DK8" t="n">
         <v>4.31</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="DM8" t="n">
         <v>57.79</v>
@@ -4148,7 +4148,7 @@
         <v>0.92</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="DP8" t="n">
         <v>5.9</v>
@@ -4696,7 +4696,7 @@
         <v>0.16</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AH10" t="n">
         <v>2.84</v>
@@ -4708,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AL10" t="n">
         <v>4.95</v>
@@ -4771,7 +4771,7 @@
         <v>1.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="BG10" t="n">
         <v>2.85</v>
@@ -4927,7 +4927,7 @@
         <v>0.2</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DG10" t="n">
         <v>2.95</v>
@@ -4939,7 +4939,7 @@
         <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="DK10" t="n">
         <v>5.57</v>
@@ -4996,7 +4996,7 @@
         <v>1.64</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="11">
@@ -5421,7 +5421,7 @@
         <v>0.22</v>
       </c>
       <c r="F12" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="G12" t="n">
         <v>2.72</v>
@@ -5433,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="K12" t="n">
         <v>4.61</v>
@@ -5496,7 +5496,7 @@
         <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.72</v>
+        <v>2.61</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5532,13 +5532,13 @@
         <v>1.74</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.95</v>
+        <v>5.74</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.53</v>
+        <v>5.05</v>
       </c>
       <c r="AT12" t="n">
         <v>1.11</v>
@@ -5562,19 +5562,19 @@
         <v>0.05</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.74</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.21</v>
+        <v>6.47</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.53</v>
+        <v>3.47</v>
       </c>
       <c r="BD12" t="n">
-        <v>11.42</v>
+        <v>12.95</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BF12" t="n">
         <v>2.05</v>
@@ -5733,7 +5733,7 @@
         <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="DG12" t="n">
         <v>2.24</v>
@@ -5745,7 +5745,7 @@
         <v>0.03</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="DK12" t="n">
         <v>4.06</v>
@@ -5763,13 +5763,13 @@
         <v>1.81</v>
       </c>
       <c r="DP12" t="n">
-        <v>7.25</v>
+        <v>7.65</v>
       </c>
       <c r="DQ12" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.22</v>
+        <v>5.48</v>
       </c>
       <c r="DS12" t="n">
         <v>0.05</v>
@@ -5787,22 +5787,22 @@
         <v>0.05</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.38</v>
+        <v>10.49</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.22</v>
+        <v>7.35</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="EA12" t="n">
-        <v>14.19</v>
+        <v>14.97</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="13">
@@ -5935,13 +5935,13 @@
         <v>2.05</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.84</v>
+        <v>7.74</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.89</v>
+        <v>6.37</v>
       </c>
       <c r="AT13" t="n">
         <v>1.58</v>
@@ -5959,25 +5959,25 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>43.53</v>
+        <v>43.58</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.16</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.109999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.68</v>
+        <v>5.84</v>
       </c>
       <c r="BC13" t="n">
         <v>3.42</v>
       </c>
       <c r="BD13" t="n">
-        <v>13.16</v>
+        <v>14.32</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BF13" t="n">
         <v>2.37</v>
@@ -6166,13 +6166,13 @@
         <v>2.05</v>
       </c>
       <c r="DP13" t="n">
-        <v>7.62</v>
+        <v>8.08</v>
       </c>
       <c r="DQ13" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.11</v>
+        <v>5.35</v>
       </c>
       <c r="DS13" t="n">
         <v>0.19</v>
@@ -6184,25 +6184,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.05</v>
+        <v>46.08</v>
       </c>
       <c r="DW13" t="n">
         <v>0.11</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.03</v>
+        <v>10.11</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.38</v>
+        <v>6.46</v>
       </c>
       <c r="DZ13" t="n">
         <v>3.65</v>
       </c>
       <c r="EA13" t="n">
-        <v>14.65</v>
+        <v>15.24</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="EC13" t="n">
         <v>2.73</v>
@@ -6227,7 +6227,7 @@
         <v>0.05</v>
       </c>
       <c r="F14" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="G14" t="n">
         <v>2.63</v>
@@ -6239,7 +6239,7 @@
         <v>0.11</v>
       </c>
       <c r="J14" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="K14" t="n">
         <v>4.47</v>
@@ -6302,7 +6302,7 @@
         <v>1.52</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6353,10 +6353,10 @@
         <v>1.22</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
         <v>-0.06</v>
@@ -6539,7 +6539,7 @@
         <v>0.03</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DG14" t="n">
         <v>2.46</v>
@@ -6551,7 +6551,7 @@
         <v>0.03</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="DK14" t="n">
         <v>4.65</v>
@@ -6578,10 +6578,10 @@
         <v>4.46</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="DU14" t="n">
         <v>-0.03</v>
@@ -6608,7 +6608,7 @@
         <v>1.51</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="15">
@@ -6741,13 +6741,13 @@
         <v>1.95</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.21</v>
+        <v>6.84</v>
       </c>
       <c r="AR15" t="n">
-        <v>1</v>
+        <v>1.37</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.37</v>
+        <v>5.11</v>
       </c>
       <c r="AT15" t="n">
         <v>1.26</v>
@@ -6765,25 +6765,25 @@
         <v>0.05</v>
       </c>
       <c r="AY15" t="n">
-        <v>46.95</v>
+        <v>46.68</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.05</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.630000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.32</v>
+        <v>5.53</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.32</v>
+        <v>3.37</v>
       </c>
       <c r="BD15" t="n">
-        <v>11.89</v>
+        <v>12.47</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BF15" t="n">
         <v>3.05</v>
@@ -6972,13 +6972,13 @@
         <v>1.97</v>
       </c>
       <c r="DP15" t="n">
-        <v>7.78</v>
+        <v>8.1</v>
       </c>
       <c r="DQ15" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.4</v>
+        <v>4.78</v>
       </c>
       <c r="DS15" t="n">
         <v>0.11</v>
@@ -6990,25 +6990,25 @@
         <v>0.05</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.84</v>
+        <v>46.7</v>
       </c>
       <c r="DW15" t="n">
         <v>0.13</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.08</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.7</v>
+        <v>5.81</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="EA15" t="n">
-        <v>13.11</v>
+        <v>13.4</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="EC15" t="n">
         <v>2.92</v>
@@ -7045,7 +7045,7 @@
         <v>0.17</v>
       </c>
       <c r="J16" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="K16" t="n">
         <v>4.61</v>
@@ -7057,19 +7057,19 @@
         <v>59.94</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="O16" t="n">
         <v>2.22</v>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>7.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="R16" t="n">
-        <v>4.17</v>
+        <v>4.61</v>
       </c>
       <c r="S16" t="n">
         <v>1.22</v>
@@ -7087,28 +7087,28 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>53.28</v>
+        <v>53.22</v>
       </c>
       <c r="Y16" t="n">
         <v>0.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.33</v>
+        <v>11.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.83</v>
+        <v>6.94</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="AC16" t="n">
-        <v>12.39</v>
+        <v>14.11</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="AF16" t="n">
         <v>0.05</v>
@@ -7357,7 +7357,7 @@
         <v>0.11</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="DK16" t="n">
         <v>5.11</v>
@@ -7369,19 +7369,19 @@
         <v>63.59</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="DO16" t="n">
         <v>2.32</v>
       </c>
       <c r="DP16" t="n">
-        <v>6.92</v>
+        <v>7.35</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="DR16" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="DS16" t="n">
         <v>0.11</v>
@@ -7393,28 +7393,28 @@
         <v>-0.03</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.71</v>
+        <v>53.68</v>
       </c>
       <c r="DW16" t="n">
         <v>0.16</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.54</v>
+        <v>11.62</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.73</v>
+        <v>6.78</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.81</v>
+        <v>4.84</v>
       </c>
       <c r="EA16" t="n">
-        <v>13.24</v>
+        <v>14.08</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
@@ -7466,13 +7466,13 @@
         <v>2.44</v>
       </c>
       <c r="P17" t="n">
-        <v>7.44</v>
+        <v>8.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="R17" t="n">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="S17" t="n">
         <v>0.9399999999999999</v>
@@ -7490,25 +7490,25 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>51.11</v>
+        <v>51.39</v>
       </c>
       <c r="Y17" t="n">
         <v>0.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.06</v>
+        <v>10.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.94</v>
+        <v>7.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.11</v>
+        <v>3.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>13.78</v>
+        <v>15.11</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
         <v>3.22</v>
@@ -7778,13 +7778,13 @@
         <v>1.94</v>
       </c>
       <c r="DP17" t="n">
-        <v>7.7</v>
+        <v>8.19</v>
       </c>
       <c r="DQ17" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="DR17" t="n">
-        <v>3.79</v>
+        <v>4.03</v>
       </c>
       <c r="DS17" t="n">
         <v>0.19</v>
@@ -7796,25 +7796,25 @@
         <v>-0.03</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.05</v>
+        <v>50.19</v>
       </c>
       <c r="DW17" t="n">
         <v>0.19</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.65</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.7</v>
+        <v>6.97</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="EA17" t="n">
-        <v>14.17</v>
+        <v>14.81</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="EC17" t="n">
         <v>2.76</v>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2025.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
